--- a/assets/Localization-Resources.xlsx
+++ b/assets/Localization-Resources.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView windowWidth="27735" windowHeight="12150"/>
   </bookViews>
   <sheets>
     <sheet name="ResXResourceManager" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="78">
   <si>
     <t>Project</t>
   </si>
@@ -252,6 +252,15 @@
   </si>
   <si>
     <t>{0}，引发了一个 “{1}” 类型的异常：{2}</t>
+  </si>
+  <si>
+    <t>FileNotFoundException_default_message</t>
+  </si>
+  <si>
+    <t>The file "{0}" not found.</t>
+  </si>
+  <si>
+    <t>未找到文件 “{0}”。</t>
   </si>
 </sst>
 </file>
@@ -1443,7 +1452,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I23"/>
+  <dimension ref="A1:I24"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="28.3" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="12.125" style="2" customWidth="1"/>
@@ -1939,6 +1948,26 @@
         <v>74</v>
       </c>
     </row>
+    <row r="24" customHeight="1" spans="1:9">
+      <c r="A24" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="I24" s="2" t="s">
+        <v>77</v>
+      </c>
+    </row>
   </sheetData>
   <sheetProtection formatColumns="0" formatRows="0" sort="0" autoFilter="0"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
